--- a/outputs/49667.xlsx
+++ b/outputs/49667.xlsx
@@ -1,53 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6880"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Edit" sheetId="3" r:id="rId1"/>
+    <sheet name="Edit" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId2"/>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+    <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="All">_xlfn.ANCHORARRAY([1]Reference!$F$2)</definedName>
-    <definedName name="BankHol">[1]!Bank_Hol[Bank Holidays]</definedName>
-    <definedName name="DateEdit">Edit!#REF!</definedName>
-    <definedName name="DateFrom">[1]Settings!$B$1</definedName>
-    <definedName name="DayDate">[1]Reference!$B$3</definedName>
-    <definedName name="DayEdit">Edit!#REF!</definedName>
-    <definedName name="fill">[2]Key!$J$4:$J$8</definedName>
-    <definedName name="GenDate">[1]Reference!$B$2</definedName>
-    <definedName name="GenName">[1]Reference!$B$1</definedName>
-    <definedName name="Head1">[1]Rota!$B$4</definedName>
-    <definedName name="Head2">OFFSET(Head1,,1)</definedName>
-    <definedName name="Head3">OFFSET(Head1,,2)</definedName>
-    <definedName name="Head4">OFFSET(Head1,,3)</definedName>
-    <definedName name="Head5">OFFSET(Head1,,4)</definedName>
-    <definedName name="Head6">OFFSET(Head1,,5)</definedName>
-    <definedName name="Head7">OFFSET(Head1,,6)</definedName>
-    <definedName name="Head8">OFFSET(Head1,,7)</definedName>
-    <definedName name="Leave">_xlfn.ANCHORARRAY([1]Reference!$G$2)</definedName>
-    <definedName name="Staff">_xlfn.ANCHORARRAY([1]Reference!$E$2)</definedName>
-    <definedName name="Start">'[1]Annual Leave'!$A$3</definedName>
-    <definedName name="WC">_xlfn.ANCHORARRAY([1]Reference!$D$2)</definedName>
+    <definedName function="false" hidden="false" name="All" vbProcedure="false">_xlfn.anchorarray([1]Reference!$F$2)</definedName>
+    <definedName function="false" hidden="false" name="BankHol" vbProcedure="false">[1]!Bank_Hol[bank holidays]</definedName>
+    <definedName function="false" hidden="false" name="DateEdit" vbProcedure="false">edit!#ref!</definedName>
+    <definedName function="false" hidden="false" name="DateFrom" vbProcedure="false">[1]Settings!$B$1</definedName>
+    <definedName function="false" hidden="false" name="DayDate" vbProcedure="false">[1]Reference!$B$3</definedName>
+    <definedName function="false" hidden="false" name="DayEdit" vbProcedure="false">edit!#ref!</definedName>
+    <definedName function="false" hidden="false" name="fill" vbProcedure="false">[2]Key!$J$4:$J$8</definedName>
+    <definedName function="false" hidden="false" name="GenDate" vbProcedure="false">[1]Reference!$B$2</definedName>
+    <definedName function="false" hidden="false" name="GenName" vbProcedure="false">[1]Reference!$B$1</definedName>
+    <definedName function="false" hidden="false" name="Head1" vbProcedure="false">[1]Rota!$B$4</definedName>
+    <definedName function="false" hidden="false" name="Head2" vbProcedure="false">OFFSET(Head1,,1)</definedName>
+    <definedName function="false" hidden="false" name="Head3" vbProcedure="false">OFFSET(Head1,,2)</definedName>
+    <definedName function="false" hidden="false" name="Head4" vbProcedure="false">OFFSET(Head1,,3)</definedName>
+    <definedName function="false" hidden="false" name="Head5" vbProcedure="false">OFFSET(Head1,,4)</definedName>
+    <definedName function="false" hidden="false" name="Head6" vbProcedure="false">OFFSET(Head1,,5)</definedName>
+    <definedName function="false" hidden="false" name="Head7" vbProcedure="false">OFFSET(Head1,,6)</definedName>
+    <definedName function="false" hidden="false" name="Head8" vbProcedure="false">OFFSET(Head1,,7)</definedName>
+    <definedName function="false" hidden="false" name="Leave" vbProcedure="false">_xlfn.anchorarray([1]Reference!$G$2)</definedName>
+    <definedName function="false" hidden="false" name="Staff" vbProcedure="false">_xlfn.anchorarray([1]Reference!$E$2)</definedName>
+    <definedName function="false" hidden="false" name="Start" vbProcedure="false">'[1]Annual Leave'!$A$3</definedName>
+    <definedName function="false" hidden="false" name="WC" vbProcedure="false">_xlfn.anchorarray([1]Reference!$D$2)</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -56,1575 +49,389 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="63">
   <si>
-    <t>Staff</t>
-  </si>
-  <si>
-    <t>Meeting Start1</t>
-  </si>
-  <si>
-    <t>Meeting Finish1</t>
-  </si>
-  <si>
-    <t>Meeting Start2</t>
-  </si>
-  <si>
-    <t>Meeting Finish2</t>
-  </si>
-  <si>
-    <t>08:00</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>Name 1</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>Name 2</t>
-  </si>
-  <si>
-    <t>Name 3</t>
-  </si>
-  <si>
-    <t>Name 4</t>
-  </si>
-  <si>
-    <t>Name 5</t>
-  </si>
-  <si>
-    <t>Name 6</t>
-  </si>
-  <si>
-    <t>Name 7</t>
-  </si>
-  <si>
-    <t>Name 8</t>
-  </si>
-  <si>
-    <t>Name 9</t>
-  </si>
-  <si>
-    <t>Name 10</t>
-  </si>
-  <si>
-    <t>Name 11</t>
-  </si>
-  <si>
-    <t>Name 12</t>
-  </si>
-  <si>
-    <t>Name 13</t>
-  </si>
-  <si>
-    <t>Name 14</t>
-  </si>
-  <si>
-    <t>Name 15</t>
+    <t xml:space="preserve">Staff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting Start1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting Finish1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting Start2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting Finish2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17:45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name 15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="h:mm"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="0"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="134"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
-    <border>
+  <borders count="2">
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="53">
+  <dxfs count="10">
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="176" formatCode="hh:mm"/>
-      <alignment horizontal="center"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="177" formatCode="hh:mm"/>
-      <alignment horizontal="center"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0088B7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="178" formatCode="hh:mm"/>
-      <alignment horizontal="center"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFA3408D"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="179" formatCode="hh:mm"/>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <scheme val="none"/>
-        <family val="2"/>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="8"/>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="center"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
         <color rgb="FF0088B7"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FF0088B7"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFA9D08E"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FF548235"/>
         </patternFill>
       </fill>
@@ -1634,68 +441,79 @@
         <color rgb="FFFFFFFF"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFA3408D"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFA6A6A6"/>
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor rgb="FFC7BBD9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color theme="4" tint="0.599963377788629"/>
-        </vertical>
-        <horizontal style="thin">
-          <color theme="4" tint="0.599963377788629"/>
-        </horizontal>
-      </border>
-    </dxf>
   </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Rota" pivot="0" count="2" xr9:uid="{EF5811ED-6B92-4EBF-B44B-D95301890C82}">
-      <tableStyleElement type="wholeTable" dxfId="52"/>
-      <tableStyleElement type="headerRow" dxfId="51"/>
-    </tableStyle>
-  </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF548235"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF0088B7"/>
+      <rgbColor rgb="FFA9D08E"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FFA3408D"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FFA6A6A6"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1718,15 +536,15 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
       <sheetData sheetId="8"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1758,68 +576,67 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Edit" displayName="Edit" ref="A1:AT16" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Edit" displayName="Edit" ref="A1:AT16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <tableColumns count="46">
-    <tableColumn id="1" name="Staff" dataDxfId="0"/>
-    <tableColumn id="10" name="Meeting Start1" dataDxfId="1"/>
-    <tableColumn id="11" name="Meeting Finish1" dataDxfId="2"/>
-    <tableColumn id="68" name="Meeting Start2" dataDxfId="3"/>
-    <tableColumn id="69" name="Meeting Finish2" dataDxfId="4"/>
-    <tableColumn id="19" name="08:00" dataDxfId="5"/>
-    <tableColumn id="20" name="08:15" dataDxfId="6"/>
-    <tableColumn id="21" name="08:30" dataDxfId="7"/>
-    <tableColumn id="22" name="08:45" dataDxfId="8"/>
-    <tableColumn id="23" name="09:00" dataDxfId="9"/>
-    <tableColumn id="24" name="09:15" dataDxfId="10"/>
-    <tableColumn id="25" name="09:30" dataDxfId="11"/>
-    <tableColumn id="26" name="09:45" dataDxfId="12"/>
-    <tableColumn id="27" name="10:00" dataDxfId="13"/>
-    <tableColumn id="28" name="10:15" dataDxfId="14"/>
-    <tableColumn id="29" name="10:30" dataDxfId="15"/>
-    <tableColumn id="30" name="10:45" dataDxfId="16"/>
-    <tableColumn id="31" name="11:00" dataDxfId="17"/>
-    <tableColumn id="32" name="11:15" dataDxfId="18"/>
-    <tableColumn id="33" name="11:30" dataDxfId="19"/>
-    <tableColumn id="34" name="11:45" dataDxfId="20"/>
-    <tableColumn id="35" name="12:00" dataDxfId="21"/>
-    <tableColumn id="36" name="12:15" dataDxfId="22"/>
-    <tableColumn id="37" name="12:30" dataDxfId="23"/>
-    <tableColumn id="38" name="12:45" dataDxfId="24"/>
-    <tableColumn id="39" name="13:00" dataDxfId="25"/>
-    <tableColumn id="40" name="13:15" dataDxfId="26"/>
-    <tableColumn id="41" name="13:30" dataDxfId="27"/>
-    <tableColumn id="42" name="13:45" dataDxfId="28"/>
-    <tableColumn id="43" name="14:00" dataDxfId="29"/>
-    <tableColumn id="44" name="14:15" dataDxfId="30"/>
-    <tableColumn id="45" name="14:30" dataDxfId="31"/>
-    <tableColumn id="46" name="14:45" dataDxfId="32"/>
-    <tableColumn id="47" name="15:00" dataDxfId="33"/>
-    <tableColumn id="48" name="15:15" dataDxfId="34"/>
-    <tableColumn id="49" name="15:30" dataDxfId="35"/>
-    <tableColumn id="50" name="15:45" dataDxfId="36"/>
-    <tableColumn id="51" name="16:00" dataDxfId="37"/>
-    <tableColumn id="52" name="16:15" dataDxfId="38"/>
-    <tableColumn id="53" name="16:30" dataDxfId="39"/>
-    <tableColumn id="54" name="16:45" dataDxfId="40"/>
-    <tableColumn id="55" name="17:00" dataDxfId="41"/>
-    <tableColumn id="56" name="17:15" dataDxfId="42"/>
-    <tableColumn id="57" name="17:30" dataDxfId="43"/>
-    <tableColumn id="58" name="17:45" dataDxfId="44"/>
-    <tableColumn id="59" name="18:00" dataDxfId="45"/>
+    <tableColumn id="1" name="Staff"/>
+    <tableColumn id="2" name="Meeting Start1"/>
+    <tableColumn id="3" name="Meeting Finish1"/>
+    <tableColumn id="4" name="Meeting Start2"/>
+    <tableColumn id="5" name="Meeting Finish2"/>
+    <tableColumn id="6" name="08:00"/>
+    <tableColumn id="7" name="08:15"/>
+    <tableColumn id="8" name="08:30"/>
+    <tableColumn id="9" name="08:45"/>
+    <tableColumn id="10" name="09:00"/>
+    <tableColumn id="11" name="09:15"/>
+    <tableColumn id="12" name="09:30"/>
+    <tableColumn id="13" name="09:45"/>
+    <tableColumn id="14" name="10:00"/>
+    <tableColumn id="15" name="10:15"/>
+    <tableColumn id="16" name="10:30"/>
+    <tableColumn id="17" name="10:45"/>
+    <tableColumn id="18" name="11:00"/>
+    <tableColumn id="19" name="11:15"/>
+    <tableColumn id="20" name="11:30"/>
+    <tableColumn id="21" name="11:45"/>
+    <tableColumn id="22" name="12:00"/>
+    <tableColumn id="23" name="12:15"/>
+    <tableColumn id="24" name="12:30"/>
+    <tableColumn id="25" name="12:45"/>
+    <tableColumn id="26" name="13:00"/>
+    <tableColumn id="27" name="13:15"/>
+    <tableColumn id="28" name="13:30"/>
+    <tableColumn id="29" name="13:45"/>
+    <tableColumn id="30" name="14:00"/>
+    <tableColumn id="31" name="14:15"/>
+    <tableColumn id="32" name="14:30"/>
+    <tableColumn id="33" name="14:45"/>
+    <tableColumn id="34" name="15:00"/>
+    <tableColumn id="35" name="15:15"/>
+    <tableColumn id="36" name="15:30"/>
+    <tableColumn id="37" name="15:45"/>
+    <tableColumn id="38" name="16:00"/>
+    <tableColumn id="39" name="16:15"/>
+    <tableColumn id="40" name="16:30"/>
+    <tableColumn id="41" name="16:45"/>
+    <tableColumn id="42" name="17:00"/>
+    <tableColumn id="43" name="17:15"/>
+    <tableColumn id="44" name="17:30"/>
+    <tableColumn id="45" name="17:45"/>
+    <tableColumn id="46" name="18:00"/>
   </tableColumns>
-  <tableStyleInfo name="Rota" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -1854,119 +671,55 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
                 <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
                 <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
                 <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
                 <a:lumMod val="102000"/>
                 <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
                 <a:lumMod val="100000"/>
                 <a:shade val="100000"/>
               </a:schemeClr>
@@ -1974,33 +727,24 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
                 <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
@@ -2013,13 +757,7 @@
           <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -2029,15 +767,13 @@
         <a:solidFill>
           <a:schemeClr val="phClr">
             <a:tint val="95000"/>
-            <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
               </a:schemeClr>
@@ -2045,7 +781,6 @@
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
               </a:schemeClr>
@@ -2053,48 +788,49 @@
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="63000"/>
-                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr codeName="Sheet8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:AT16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="10"/>
+  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="9.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.8583333333333" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.8583333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="11.425" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.2833333333333" style="2" customWidth="1"/>
-    <col min="6" max="47" width="4.70833333333333" style="2" customWidth="1"/>
-    <col min="48" max="16384" width="9.14166666666667" style="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="6" style="1" width="4.71"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="48" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="25.5" customHeight="1" spans="1:46">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="3" customFormat="true" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -2221,20 +957,20 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:46">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="6" t="n">
         <v>0.46875</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="6" t="n">
         <v>0.510416666666667</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="6" t="n">
         <v>0.572916666666667</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="6" t="n">
         <v>0.614583333333333</v>
       </c>
       <c r="F2" s="7"/>
@@ -2345,14 +1081,14 @@
       <c r="AS2" s="8"/>
       <c r="AT2" s="8"/>
     </row>
-    <row r="3" spans="1:46">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="6" t="n">
         <v>0.4375</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="6" t="n">
         <v>0.4375</v>
       </c>
       <c r="D3" s="6"/>
@@ -2465,8 +1201,8 @@
       <c r="AS3" s="8"/>
       <c r="AT3" s="8"/>
     </row>
-    <row r="4" spans="1:46">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B4" s="6"/>
@@ -2581,14 +1317,14 @@
       <c r="AS4" s="8"/>
       <c r="AT4" s="8"/>
     </row>
-    <row r="5" spans="1:46">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="6" t="n">
         <v>0.333333333333333</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="6" t="n">
         <v>0.666666666666667</v>
       </c>
       <c r="D5" s="6"/>
@@ -2701,8 +1437,8 @@
       <c r="AS5" s="8"/>
       <c r="AT5" s="8"/>
     </row>
-    <row r="6" spans="1:46">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B6" s="6"/>
@@ -2817,16 +1553,22 @@
       <c r="AS6" s="8"/>
       <c r="AT6" s="8"/>
     </row>
-    <row r="7" spans="1:46">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="6" t="n">
         <v>0.4375</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="C7" s="6" t="n">
+        <v>0.458333333333333</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.572916666666667</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.635416666666667</v>
+      </c>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
@@ -2935,8 +1677,8 @@
       <c r="AS7" s="8"/>
       <c r="AT7" s="8"/>
     </row>
-    <row r="8" spans="1:46">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B8" s="6"/>
@@ -3051,8 +1793,8 @@
       <c r="AS8" s="8"/>
       <c r="AT8" s="8"/>
     </row>
-    <row r="9" spans="1:46">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B9" s="6"/>
@@ -3167,14 +1909,16 @@
       <c r="AS9" s="8"/>
       <c r="AT9" s="8"/>
     </row>
-    <row r="10" spans="1:46">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="6" t="n">
         <v>0.510416666666667</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="6" t="n">
+        <v>0.541666666666667</v>
+      </c>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="7" t="s">
@@ -3285,8 +2029,8 @@
       <c r="AS10" s="8"/>
       <c r="AT10" s="8"/>
     </row>
-    <row r="11" spans="1:46">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B11" s="6"/>
@@ -3401,8 +2145,8 @@
       <c r="AS11" s="8"/>
       <c r="AT11" s="8"/>
     </row>
-    <row r="12" spans="1:46">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B12" s="6"/>
@@ -3517,8 +2261,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:46">
-      <c r="A13" s="2" t="s">
+    <row r="13" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B13" s="6"/>
@@ -3633,14 +2377,22 @@
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:46">
-      <c r="A14" s="2" t="s">
+    <row r="14" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
+      <c r="B14" s="6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.541666666666667</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.552083333333333</v>
+      </c>
       <c r="F14" s="7"/>
       <c r="G14" s="8"/>
       <c r="H14" s="8"/>
@@ -3749,8 +2501,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:46">
-      <c r="A15" s="2" t="s">
+    <row r="15" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="6"/>
@@ -3865,8 +2617,8 @@
       <c r="AS15" s="8"/>
       <c r="AT15" s="8"/>
     </row>
-    <row r="16" spans="1:46">
-      <c r="A16" s="2" t="s">
+    <row r="16" customFormat="false" ht="11.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B16" s="6"/>
@@ -3967,29 +2719,33 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:AT16">
-    <cfRule type="cellIs" dxfId="46" priority="13" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"x"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="14" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"b"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="15" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>"l"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="16" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"m"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="17" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>"AL"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="18" stopIfTrue="1" operator="equal">
+    <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>"NWD"</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <tableParts count="1">
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <tableParts>
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>

--- a/outputs/49667.xlsx
+++ b/outputs/49667.xlsx
@@ -965,13 +965,13 @@
         <v>0.46875</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>0.510416666666667</v>
+        <v>0.479166666666667</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>0.572916666666667</v>
+        <v>0.489583333333333</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>0.614583333333333</v>
+        <v>0.5</v>
       </c>
       <c r="F2" s="7"/>
       <c r="G2" s="8"/>
@@ -1325,10 +1325,14 @@
         <v>0.333333333333333</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0.666666666666667</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
+        <v>0.34375</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.354166666666667</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0.364583333333333</v>
+      </c>
       <c r="F5" s="8" t="s">
         <v>48</v>
       </c>
@@ -1561,13 +1565,13 @@
         <v>0.4375</v>
       </c>
       <c r="C7" s="6" t="n">
+        <v>0.447916666666667</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>0.458333333333333</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>0.572916666666667</v>
-      </c>
       <c r="E7" s="6" t="n">
-        <v>0.635416666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="8"/>
@@ -1917,10 +1921,14 @@
         <v>0.510416666666667</v>
       </c>
       <c r="C10" s="6" t="n">
+        <v>0.520833333333333</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="E10" s="6" t="n">
         <v>0.541666666666667</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
       <c r="F10" s="7" t="s">
         <v>47</v>
       </c>
@@ -2385,13 +2393,13 @@
         <v>0.4375</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>0.4375</v>
+        <v>0.541666666666667</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>0.541666666666667</v>
+        <v>0.552083333333333</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>0.552083333333333</v>
+        <v>0.5625</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="8"/>
